--- a/database/event/5277/event_5277_evp_summary.xlsx
+++ b/database/event/5277/event_5277_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>4.3851</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8384</v>
+        <v>3.7571</v>
       </c>
       <c r="E2" t="n">
         <v>10.5446</v>
@@ -548,7 +548,7 @@
         <v>3.2178</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7045</v>
+        <v>2.6388</v>
       </c>
       <c r="E3" t="n">
         <v>7.7378</v>
@@ -594,7 +594,7 @@
         <v>2.7898</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2887</v>
+        <v>2.2287</v>
       </c>
       <c r="E4" t="n">
         <v>6.7084</v>
@@ -640,7 +640,7 @@
         <v>2.746</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2461</v>
+        <v>2.1868</v>
       </c>
       <c r="E5" t="n">
         <v>6.6031</v>
@@ -686,7 +686,7 @@
         <v>2.6879</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E6" t="n">
         <v>6.4635</v>
@@ -732,7 +732,7 @@
         <v>2.6738</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1761</v>
+        <v>2.1176</v>
       </c>
       <c r="E7" t="n">
         <v>6.4296</v>
@@ -778,7 +778,7 @@
         <v>2.6399</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1431</v>
+        <v>2.0851</v>
       </c>
       <c r="E8" t="n">
         <v>6.348</v>
@@ -824,7 +824,7 @@
         <v>2.6292</v>
       </c>
       <c r="D9" t="n">
-        <v>2.1327</v>
+        <v>2.0749</v>
       </c>
       <c r="E9" t="n">
         <v>6.3222</v>
@@ -870,7 +870,7 @@
         <v>2.5535</v>
       </c>
       <c r="D10" t="n">
-        <v>2.0591</v>
+        <v>2.0023</v>
       </c>
       <c r="E10" t="n">
         <v>6.1402</v>
@@ -916,7 +916,7 @@
         <v>2.5089</v>
       </c>
       <c r="D11" t="n">
-        <v>2.0158</v>
+        <v>1.9596</v>
       </c>
       <c r="E11" t="n">
         <v>6.033</v>
@@ -962,7 +962,7 @@
         <v>2.4107</v>
       </c>
       <c r="D12" t="n">
-        <v>1.9205</v>
+        <v>1.8656</v>
       </c>
       <c r="E12" t="n">
         <v>5.797</v>
@@ -1008,7 +1008,7 @@
         <v>2.3923</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9026</v>
+        <v>1.848</v>
       </c>
       <c r="E13" t="n">
         <v>5.7527</v>
@@ -1054,7 +1054,7 @@
         <v>2.3889</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8993</v>
+        <v>1.8447</v>
       </c>
       <c r="E14" t="n">
         <v>5.7445</v>
@@ -1100,7 +1100,7 @@
         <v>2.3471</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8587</v>
+        <v>1.8047</v>
       </c>
       <c r="E15" t="n">
         <v>5.644</v>
@@ -1146,7 +1146,7 @@
         <v>2.2819</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7953</v>
+        <v>1.7422</v>
       </c>
       <c r="E16" t="n">
         <v>5.4872</v>
@@ -1192,7 +1192,7 @@
         <v>2.2245</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7396</v>
+        <v>1.6872</v>
       </c>
       <c r="E17" t="n">
         <v>5.3492</v>
@@ -1238,7 +1238,7 @@
         <v>2.2156</v>
       </c>
       <c r="D18" t="n">
-        <v>1.731</v>
+        <v>1.6787</v>
       </c>
       <c r="E18" t="n">
         <v>5.3278</v>
@@ -1284,7 +1284,7 @@
         <v>2.2144</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7297</v>
+        <v>1.6775</v>
       </c>
       <c r="E19" t="n">
         <v>5.3248</v>
@@ -1330,7 +1330,7 @@
         <v>2.1737</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6902</v>
+        <v>1.6385</v>
       </c>
       <c r="E20" t="n">
         <v>5.227</v>
@@ -1376,7 +1376,7 @@
         <v>2.0462</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5664</v>
+        <v>1.5164</v>
       </c>
       <c r="E21" t="n">
         <v>4.9204</v>
@@ -1422,7 +1422,7 @@
         <v>2.0007</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5222</v>
+        <v>1.4728</v>
       </c>
       <c r="E22" t="n">
         <v>4.811</v>
@@ -1468,7 +1468,7 @@
         <v>1.9897</v>
       </c>
       <c r="D23" t="n">
-        <v>1.5115</v>
+        <v>1.4623</v>
       </c>
       <c r="E23" t="n">
         <v>4.7846</v>
@@ -1514,7 +1514,7 @@
         <v>1.9762</v>
       </c>
       <c r="D24" t="n">
-        <v>1.4983</v>
+        <v>1.4493</v>
       </c>
       <c r="E24" t="n">
         <v>4.752</v>
@@ -1560,7 +1560,7 @@
         <v>1.9588</v>
       </c>
       <c r="D25" t="n">
-        <v>1.4815</v>
+        <v>1.4326</v>
       </c>
       <c r="E25" t="n">
         <v>4.7102</v>
@@ -1606,7 +1606,7 @@
         <v>1.8657</v>
       </c>
       <c r="D26" t="n">
-        <v>1.391</v>
+        <v>1.3435</v>
       </c>
       <c r="E26" t="n">
         <v>4.4864</v>
@@ -1652,7 +1652,7 @@
         <v>1.8532</v>
       </c>
       <c r="D27" t="n">
-        <v>1.3788</v>
+        <v>1.3314</v>
       </c>
       <c r="E27" t="n">
         <v>4.4562</v>
@@ -1698,7 +1698,7 @@
         <v>1.7848</v>
       </c>
       <c r="D28" t="n">
-        <v>1.3124</v>
+        <v>1.2659</v>
       </c>
       <c r="E28" t="n">
         <v>4.2917</v>
@@ -1744,7 +1744,7 @@
         <v>1.7682</v>
       </c>
       <c r="D29" t="n">
-        <v>1.2964</v>
+        <v>1.2501</v>
       </c>
       <c r="E29" t="n">
         <v>4.252</v>
@@ -1790,7 +1790,7 @@
         <v>1.7637</v>
       </c>
       <c r="D30" t="n">
-        <v>1.292</v>
+        <v>1.2458</v>
       </c>
       <c r="E30" t="n">
         <v>4.2412</v>
@@ -1836,7 +1836,7 @@
         <v>1.6905</v>
       </c>
       <c r="D31" t="n">
-        <v>1.2208</v>
+        <v>1.1756</v>
       </c>
       <c r="E31" t="n">
         <v>4.0651</v>
@@ -1882,7 +1882,7 @@
         <v>1.6868</v>
       </c>
       <c r="D32" t="n">
-        <v>1.2172</v>
+        <v>1.172</v>
       </c>
       <c r="E32" t="n">
         <v>4.0561</v>
@@ -1928,7 +1928,7 @@
         <v>1.5762</v>
       </c>
       <c r="D33" t="n">
-        <v>1.1098</v>
+        <v>1.0661</v>
       </c>
       <c r="E33" t="n">
         <v>3.7901</v>
@@ -1974,7 +1974,7 @@
         <v>1.5356</v>
       </c>
       <c r="D34" t="n">
-        <v>1.0703</v>
+        <v>1.0272</v>
       </c>
       <c r="E34" t="n">
         <v>3.6925</v>
@@ -2020,7 +2020,7 @@
         <v>1.4823</v>
       </c>
       <c r="D35" t="n">
-        <v>1.0186</v>
+        <v>0.9761</v>
       </c>
       <c r="E35" t="n">
         <v>3.5644</v>
@@ -2066,7 +2066,7 @@
         <v>1.4612</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9981</v>
+        <v>0.9559</v>
       </c>
       <c r="E36" t="n">
         <v>3.5136</v>
@@ -2112,7 +2112,7 @@
         <v>1.4155</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9537</v>
+        <v>0.9122</v>
       </c>
       <c r="E37" t="n">
         <v>3.4039</v>
@@ -2158,7 +2158,7 @@
         <v>1.4046</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9431</v>
+        <v>0.9016999999999999</v>
       </c>
       <c r="E38" t="n">
         <v>3.3776</v>
@@ -2204,7 +2204,7 @@
         <v>1.3906</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9295</v>
+        <v>0.8883</v>
       </c>
       <c r="E39" t="n">
         <v>3.3439</v>
@@ -2250,7 +2250,7 @@
         <v>1.3649</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9045</v>
+        <v>0.8637</v>
       </c>
       <c r="E40" t="n">
         <v>3.2821</v>
@@ -2296,7 +2296,7 @@
         <v>1.3281</v>
       </c>
       <c r="D41" t="n">
-        <v>0.8687</v>
+        <v>0.8284</v>
       </c>
       <c r="E41" t="n">
         <v>3.1935</v>
@@ -2342,7 +2342,7 @@
         <v>1.3272</v>
       </c>
       <c r="D42" t="n">
-        <v>0.8679</v>
+        <v>0.8276</v>
       </c>
       <c r="E42" t="n">
         <v>3.1915</v>
@@ -2388,7 +2388,7 @@
         <v>1.277</v>
       </c>
       <c r="D43" t="n">
-        <v>0.8192</v>
+        <v>0.7795</v>
       </c>
       <c r="E43" t="n">
         <v>3.0708</v>
@@ -2434,7 +2434,7 @@
         <v>1.1526</v>
       </c>
       <c r="D44" t="n">
-        <v>0.6983</v>
+        <v>0.6603</v>
       </c>
       <c r="E44" t="n">
         <v>2.7717</v>
@@ -2480,7 +2480,7 @@
         <v>1.1357</v>
       </c>
       <c r="D45" t="n">
-        <v>0.6819</v>
+        <v>0.6441</v>
       </c>
       <c r="E45" t="n">
         <v>2.731</v>
@@ -2526,7 +2526,7 @@
         <v>0.7431</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3005</v>
+        <v>0.268</v>
       </c>
       <c r="E46" t="n">
         <v>1.7868</v>
@@ -2572,7 +2572,7 @@
         <v>0.72</v>
       </c>
       <c r="D47" t="n">
-        <v>0.278</v>
+        <v>0.2458</v>
       </c>
       <c r="E47" t="n">
         <v>1.7313</v>
@@ -2618,7 +2618,7 @@
         <v>0.511</v>
       </c>
       <c r="D48" t="n">
-        <v>0.075</v>
+        <v>0.0456</v>
       </c>
       <c r="E48" t="n">
         <v>1.2287</v>
@@ -2664,7 +2664,7 @@
         <v>0.4866</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0514</v>
+        <v>0.0223</v>
       </c>
       <c r="E49" t="n">
         <v>1.1702</v>
@@ -2710,7 +2710,7 @@
         <v>0.3335</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.0974</v>
+        <v>-0.1244</v>
       </c>
       <c r="E50" t="n">
         <v>0.802</v>
@@ -2756,7 +2756,7 @@
         <v>0.2644</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.1645</v>
+        <v>-0.1906</v>
       </c>
       <c r="E51" t="n">
         <v>0.6359</v>
@@ -2802,7 +2802,7 @@
         <v>0.2237</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.2041</v>
+        <v>-0.2296</v>
       </c>
       <c r="E52" t="n">
         <v>0.5379</v>
@@ -2848,7 +2848,7 @@
         <v>0.2028</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.2243</v>
+        <v>-0.2496</v>
       </c>
       <c r="E53" t="n">
         <v>0.4877</v>
@@ -2894,7 +2894,7 @@
         <v>0.1935</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.2334</v>
+        <v>-0.2585</v>
       </c>
       <c r="E54" t="n">
         <v>0.4654</v>
@@ -2940,7 +2940,7 @@
         <v>0.0849</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.3389</v>
+        <v>-0.3626</v>
       </c>
       <c r="E55" t="n">
         <v>0.2042</v>
@@ -2986,7 +2986,7 @@
         <v>0.0653</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.3579</v>
+        <v>-0.3813</v>
       </c>
       <c r="E56" t="n">
         <v>0.1571</v>
@@ -3032,7 +3032,7 @@
         <v>0.0012</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4202</v>
+        <v>-0.4428</v>
       </c>
       <c r="E57" t="n">
         <v>0.0029</v>
@@ -3078,7 +3078,7 @@
         <v>-0.0502</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4701</v>
+        <v>-0.492</v>
       </c>
       <c r="E58" t="n">
         <v>-0.1206</v>
@@ -3124,7 +3124,7 @@
         <v>-0.153</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5699</v>
+        <v>-0.5904</v>
       </c>
       <c r="E59" t="n">
         <v>-0.3678</v>
@@ -3170,7 +3170,7 @@
         <v>-0.1804</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5966</v>
+        <v>-0.6167</v>
       </c>
       <c r="E60" t="n">
         <v>-0.4337</v>
@@ -3216,7 +3216,7 @@
         <v>-0.1955</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6113</v>
+        <v>-0.6312</v>
       </c>
       <c r="E61" t="n">
         <v>-0.4701</v>
@@ -3262,7 +3262,7 @@
         <v>-0.234</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.6681</v>
       </c>
       <c r="E62" t="n">
         <v>-0.5627</v>
@@ -3308,7 +3308,7 @@
         <v>-0.4738</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8817</v>
+        <v>-0.8978</v>
       </c>
       <c r="E63" t="n">
         <v>-1.1394</v>
@@ -3354,7 +3354,7 @@
         <v>-0.5612</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.9666</v>
+        <v>-0.9816</v>
       </c>
       <c r="E64" t="n">
         <v>-1.3496</v>
@@ -3400,7 +3400,7 @@
         <v>-0.5711000000000001</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.9761</v>
+        <v>-0.991</v>
       </c>
       <c r="E65" t="n">
         <v>-1.3732</v>
@@ -3446,7 +3446,7 @@
         <v>-0.6348</v>
       </c>
       <c r="D66" t="n">
-        <v>-1.038</v>
+        <v>-1.0521</v>
       </c>
       <c r="E66" t="n">
         <v>-1.5265</v>
@@ -3492,7 +3492,7 @@
         <v>-0.6664</v>
       </c>
       <c r="D67" t="n">
-        <v>-1.0687</v>
+        <v>-1.0823</v>
       </c>
       <c r="E67" t="n">
         <v>-1.6024</v>
@@ -3538,7 +3538,7 @@
         <v>-0.8508</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.2479</v>
+        <v>-1.259</v>
       </c>
       <c r="E68" t="n">
         <v>-2.0459</v>
@@ -3584,7 +3584,7 @@
         <v>-0.8817</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.2779</v>
+        <v>-1.2886</v>
       </c>
       <c r="E69" t="n">
         <v>-2.1202</v>
@@ -3630,7 +3630,7 @@
         <v>-1.0164</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.4087</v>
+        <v>-1.4176</v>
       </c>
       <c r="E70" t="n">
         <v>-2.444</v>
@@ -3676,7 +3676,7 @@
         <v>-1.3838</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.7656</v>
+        <v>-1.7696</v>
       </c>
       <c r="E71" t="n">
         <v>-3.3275</v>
@@ -3722,7 +3722,7 @@
         <v>-1.4765</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.8557</v>
+        <v>-1.8584</v>
       </c>
       <c r="E72" t="n">
         <v>-3.5505</v>
@@ -3768,7 +3768,7 @@
         <v>-1.6669</v>
       </c>
       <c r="D73" t="n">
-        <v>-2.0406</v>
+        <v>-2.0408</v>
       </c>
       <c r="E73" t="n">
         <v>-4.0082</v>
@@ -3814,7 +3814,7 @@
         <v>-1.7306</v>
       </c>
       <c r="D74" t="n">
-        <v>-2.1025</v>
+        <v>-2.1018</v>
       </c>
       <c r="E74" t="n">
         <v>-4.1614</v>
@@ -3860,7 +3860,7 @@
         <v>-1.7576</v>
       </c>
       <c r="D75" t="n">
-        <v>-2.1288</v>
+        <v>-2.1277</v>
       </c>
       <c r="E75" t="n">
         <v>-4.2265</v>
@@ -3906,7 +3906,7 @@
         <v>-1.7609</v>
       </c>
       <c r="D76" t="n">
-        <v>-2.1319</v>
+        <v>-2.1309</v>
       </c>
       <c r="E76" t="n">
         <v>-4.2343</v>
@@ -3952,7 +3952,7 @@
         <v>-2.1574</v>
       </c>
       <c r="D77" t="n">
-        <v>-2.5171</v>
+        <v>-2.5107</v>
       </c>
       <c r="E77" t="n">
         <v>-5.1878</v>
@@ -3998,7 +3998,7 @@
         <v>-2.2184</v>
       </c>
       <c r="D78" t="n">
-        <v>-2.5764</v>
+        <v>-2.5692</v>
       </c>
       <c r="E78" t="n">
         <v>-5.3345</v>
@@ -4044,7 +4044,7 @@
         <v>-2.2407</v>
       </c>
       <c r="D79" t="n">
-        <v>-2.5981</v>
+        <v>-2.5906</v>
       </c>
       <c r="E79" t="n">
         <v>-5.3882</v>
@@ -4090,7 +4090,7 @@
         <v>-2.4029</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.7556</v>
+        <v>-2.7459</v>
       </c>
       <c r="E80" t="n">
         <v>-5.7781</v>
@@ -4136,7 +4136,7 @@
         <v>-2.5036</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.8535</v>
+        <v>-2.8424</v>
       </c>
       <c r="E81" t="n">
         <v>-6.0204</v>
@@ -4182,7 +4182,7 @@
         <v>-3.1305</v>
       </c>
       <c r="D82" t="n">
-        <v>-3.4624</v>
+        <v>-3.4429</v>
       </c>
       <c r="E82" t="n">
         <v>-7.5277</v>
